--- a/sub_pro_16_wc_2026_pred/datasets/tsi_1_prediction.xlsx
+++ b/sub_pro_16_wc_2026_pred/datasets/tsi_1_prediction.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.0207845382367461</v>
+        <v>0.01912935308661114</v>
       </c>
     </row>
     <row r="3">
@@ -398,7 +398,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.8548399914356649</v>
+        <v>-0.8570637184182824</v>
       </c>
     </row>
     <row r="4">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.2758490633732051</v>
+        <v>-0.279156577695426</v>
       </c>
     </row>
     <row r="5">
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.4457009881794206</v>
+        <v>-0.4496755375224776</v>
       </c>
     </row>
     <row r="6">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.2246084442112423</v>
+        <v>-0.2308754385993757</v>
       </c>
     </row>
     <row r="7">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.6943969221649914</v>
+        <v>-0.6980471676971793</v>
       </c>
     </row>
     <row r="8">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.783632194509278</v>
+        <v>-0.784060459016892</v>
       </c>
     </row>
     <row r="9">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.3417120492814776</v>
+        <v>0.3373750781289953</v>
       </c>
     </row>
     <row r="10">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>1.163707161080032</v>
+        <v>1.16280868048747</v>
       </c>
     </row>
     <row r="11">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.2751757899499714</v>
+        <v>0.2729462134932739</v>
       </c>
     </row>
     <row r="12">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.842676957614203</v>
+        <v>-0.8436627983406334</v>
       </c>
     </row>
     <row r="13">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.2973612190345263</v>
+        <v>-0.3012089379547098</v>
       </c>
     </row>
     <row r="14">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.4341702812674287</v>
+        <v>0.4303698662056457</v>
       </c>
     </row>
     <row r="15">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.3046339471193304</v>
+        <v>-0.3058079405354814</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.2778491376861812</v>
+        <v>-0.1569575817598915</v>
       </c>
     </row>
     <row r="17">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.1159185455440597</v>
+        <v>0.1125000065230675</v>
       </c>
     </row>
     <row r="18">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.9118050604621586</v>
+        <v>0.9080149272968749</v>
       </c>
     </row>
     <row r="19">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.891946811329312</v>
+        <v>-0.8922985697035638</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.001423566547240587</v>
+        <v>-0.002070919607596811</v>
       </c>
     </row>
     <row r="21">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.0906810566714083</v>
+        <v>0.08905269570951915</v>
       </c>
     </row>
     <row r="22">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.860368746170681</v>
+        <v>0.8567568322560222</v>
       </c>
     </row>
     <row r="23">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.16169767314103</v>
+        <v>0.1551510213512325</v>
       </c>
     </row>
     <row r="24">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.09531492603379491</v>
+        <v>-0.1002549126612468</v>
       </c>
     </row>
     <row r="25">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.6414582790205635</v>
+        <v>-0.6432559231973891</v>
       </c>
     </row>
     <row r="26">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.4908844627531633</v>
+        <v>0.4873019017338803</v>
       </c>
     </row>
     <row r="27">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.4330128172352374</v>
+        <v>-0.4343394012885332</v>
       </c>
     </row>
     <row r="28">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.4463379108015591</v>
+        <v>-0.4485410445239205</v>
       </c>
     </row>
     <row r="29">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.8550487583966596</v>
+        <v>-0.8586754640080289</v>
       </c>
     </row>
     <row r="30">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>1.706931952570343</v>
+        <v>1.703773944738151</v>
       </c>
     </row>
     <row r="31">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.7496087410287837</v>
+        <v>-0.7510351224640026</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.7394593669798071</v>
+        <v>-0.7402733116284399</v>
       </c>
     </row>
     <row r="33">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.1587711104826316</v>
+        <v>0.1565161586876387</v>
       </c>
     </row>
     <row r="34">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>1.993706843024397</v>
+        <v>1.990298095683283</v>
       </c>
     </row>
     <row r="35">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.2475486054302884</v>
+        <v>0.2472844571187766</v>
       </c>
     </row>
     <row r="36">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.7065855579102811</v>
+        <v>-0.7079419464701759</v>
       </c>
     </row>
     <row r="37">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.4394248496930133</v>
+        <v>0.4343047860941786</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>1.105541185228257</v>
+        <v>1.102439826581688</v>
       </c>
     </row>
     <row r="39">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.1872042093655318</v>
+        <v>-0.1884371654038261</v>
       </c>
     </row>
     <row r="40">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>-0.05070204011524204</v>
+        <v>-0.05487395278180981</v>
       </c>
     </row>
     <row r="41">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.7709833289348683</v>
+        <v>-0.7728705578765632</v>
       </c>
     </row>
     <row r="42">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>1.171569662991861</v>
+        <v>1.168925884770143</v>
       </c>
     </row>
     <row r="43">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.4171759973621708</v>
+        <v>-0.4182711325912036</v>
       </c>
     </row>
     <row r="44">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.6581074256735472</v>
+        <v>-0.6612731171194991</v>
       </c>
     </row>
     <row r="45">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.2507454182225939</v>
+        <v>0.2497700699955107</v>
       </c>
     </row>
     <row r="46">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>1.552263162576021</v>
+        <v>1.548406996524726</v>
       </c>
     </row>
     <row r="47">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.1961688544602793</v>
+        <v>0.19281567718564</v>
       </c>
     </row>
     <row r="48">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>-0.6180098783277844</v>
+        <v>-0.6185008247952056</v>
       </c>
     </row>
     <row r="49">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.4256485288474209</v>
+        <v>-0.4265129499909797</v>
       </c>
     </row>
   </sheetData>
